--- a/mistral_translate_work/split_by_prompt/excel/name_title/lang_multi_text/lang_multi_text__name_title__part_0114.xlsx
+++ b/mistral_translate_work/split_by_prompt/excel/name_title/lang_multi_text/lang_multi_text__name_title__part_0114.xlsx
@@ -2744,7 +2744,7 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>Đánh bại Void Storm TD</t>
+          <t>Hạ gục Void Storm TDs</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
@@ -2814,7 +2814,7 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>Nhiệm vụ Khám phá</t>
+          <t>Nhiệm Vụ Thám Hiểm</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
@@ -2884,7 +2884,7 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>Thu thập Thế giới mở ở Lahai-Roi</t>
+          <t>Bộ Sưu Tập Thế Giới Mở tại Lahai-Roi</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
@@ -2954,7 +2954,7 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>Sự kiện và Nhiệm vụ ở Lahai-Roi</t>
+          <t>Sự kiện và Nhiệm vụ tại Lahai-Roi</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
@@ -8064,7 +8064,7 @@
       </c>
       <c r="M109" t="inlineStr">
         <is>
-          <t>Ink Black</t>
+          <t>Đen như mực</t>
         </is>
       </c>
       <c r="N109" t="inlineStr">
@@ -8134,7 +8134,7 @@
       </c>
       <c r="M110" t="inlineStr">
         <is>
-          <t>Blue Indigo</t>
+          <t>Chàm Xanh</t>
         </is>
       </c>
       <c r="N110" t="inlineStr">
@@ -8204,7 +8204,7 @@
       </c>
       <c r="M111" t="inlineStr">
         <is>
-          <t>Deep Purple</t>
+          <t>Tím Đậm</t>
         </is>
       </c>
       <c r="N111" t="inlineStr">
@@ -8344,7 +8344,7 @@
       </c>
       <c r="M113" t="inlineStr">
         <is>
-          <t>Bright Yellow</t>
+          <t>Vàng Rực Rỡ</t>
         </is>
       </c>
       <c r="N113" t="inlineStr">
@@ -8624,7 +8624,7 @@
       </c>
       <c r="M117" t="inlineStr">
         <is>
-          <t>Lemming Charge</t>
+          <t>Tấn Công Đàn Cừu</t>
         </is>
       </c>
       <c r="N117" t="inlineStr">
@@ -9954,7 +9954,7 @@
       </c>
       <c r="M136" t="inlineStr">
         <is>
-          <t>Carefree Rainbow</t>
+          <t>Cầu vồng thảnh thơi</t>
         </is>
       </c>
       <c r="N136" t="inlineStr">
@@ -10024,7 +10024,7 @@
       </c>
       <c r="M137" t="inlineStr">
         <is>
-          <t>Farewell to Yesterday</t>
+          <t>Tạm biệt ngày hôm qua</t>
         </is>
       </c>
       <c r="N137" t="inlineStr">
@@ -10094,7 +10094,7 @@
       </c>
       <c r="M138" t="inlineStr">
         <is>
-          <t>Cube Expert</t>
+          <t>Chuyên Gia Khối</t>
         </is>
       </c>
       <c r="N138" t="inlineStr">
@@ -10164,7 +10164,7 @@
       </c>
       <c r="M139" t="inlineStr">
         <is>
-          <t>Chuu! Chuluu?</t>
+          <t>Chíp! Chít chít?</t>
         </is>
       </c>
       <c r="N139" t="inlineStr">
@@ -10234,7 +10234,7 @@
       </c>
       <c r="M140" t="inlineStr">
         <is>
-          <t>Companionship</t>
+          <t>Tình đồng đội</t>
         </is>
       </c>
       <c r="N140" t="inlineStr">
@@ -10374,7 +10374,7 @@
       </c>
       <c r="M142" t="inlineStr">
         <is>
-          <t>Happy Soliskin Family</t>
+          <t>Gia đình Soliskin hạnh phúc</t>
         </is>
       </c>
       <c r="N142" t="inlineStr">
@@ -10444,7 +10444,7 @@
       </c>
       <c r="M143" t="inlineStr">
         <is>
-          <t>Studious Soliskin</t>
+          <t>Người Soliskin chăm chỉ</t>
         </is>
       </c>
       <c r="N143" t="inlineStr">
@@ -10514,7 +10514,7 @@
       </c>
       <c r="M144" t="inlineStr">
         <is>
-          <t>Low Fuel</t>
+          <t>Nhiên Liệu Thấp</t>
         </is>
       </c>
       <c r="N144" t="inlineStr">
@@ -10584,7 +10584,7 @@
       </c>
       <c r="M145" t="inlineStr">
         <is>
-          <t>Repletion</t>
+          <t>Sự Bổ Sung</t>
         </is>
       </c>
       <c r="N145" t="inlineStr">
@@ -10654,7 +10654,7 @@
       </c>
       <c r="M146" t="inlineStr">
         <is>
-          <t>Dhalifa's Smile</t>
+          <t>Nụ Cười Của Dhalifa</t>
         </is>
       </c>
       <c r="N146" t="inlineStr">
@@ -10724,7 +10724,7 @@
       </c>
       <c r="M147" t="inlineStr">
         <is>
-          <t>The Shimmer Comes</t>
+          <t>Ánh Lấp Lánh Tràn Tới</t>
         </is>
       </c>
       <c r="N147" t="inlineStr">
@@ -11144,7 +11144,7 @@
       </c>
       <c r="M153" t="inlineStr">
         <is>
-          <t>Shadow</t>
+          <t>Bóng Tối</t>
         </is>
       </c>
       <c r="N153" t="inlineStr">
@@ -11214,7 +11214,7 @@
       </c>
       <c r="M154" t="inlineStr">
         <is>
-          <t>Carefree Rainbow</t>
+          <t>Cầu vồng thảnh thơi</t>
         </is>
       </c>
       <c r="N154" t="inlineStr">
@@ -11284,7 +11284,7 @@
       </c>
       <c r="M155" t="inlineStr">
         <is>
-          <t>Farewell to Yesterday</t>
+          <t>Tạm biệt ngày hôm qua</t>
         </is>
       </c>
       <c r="N155" t="inlineStr">
@@ -11354,7 +11354,7 @@
       </c>
       <c r="M156" t="inlineStr">
         <is>
-          <t>Carefree Rainbow</t>
+          <t>Cầu vồng thảnh thơi</t>
         </is>
       </c>
       <c r="N156" t="inlineStr">
@@ -11424,7 +11424,7 @@
       </c>
       <c r="M157" t="inlineStr">
         <is>
-          <t>Farewell to Yesterday</t>
+          <t>Tạm biệt ngày hôm qua</t>
         </is>
       </c>
       <c r="N157" t="inlineStr">
@@ -11844,7 +11844,7 @@
       </c>
       <c r="M163" t="inlineStr">
         <is>
-          <t>Curiosity Takes Flight</t>
+          <t>Đam Mê Khám Phá</t>
         </is>
       </c>
       <c r="N163" t="inlineStr">
@@ -11914,7 +11914,7 @@
       </c>
       <c r="M164" t="inlineStr">
         <is>
-          <t>A Cozy Break</t>
+          <t>Khoảnh Khắc Thư Giãn</t>
         </is>
       </c>
       <c r="N164" t="inlineStr">
@@ -11984,7 +11984,7 @@
       </c>
       <c r="M165" t="inlineStr">
         <is>
-          <t>Warmed Up Abby</t>
+          <t>Abby Đã Khởi Động</t>
         </is>
       </c>
       <c r="N165" t="inlineStr">
@@ -12054,7 +12054,7 @@
       </c>
       <c r="M166" t="inlineStr">
         <is>
-          <t>A Fleeting Encounter</t>
+          <t>Một Cuộc Gặp Gỡ Chóng Vánh</t>
         </is>
       </c>
       <c r="N166" t="inlineStr">
@@ -12194,7 +12194,7 @@
       </c>
       <c r="M168" t="inlineStr">
         <is>
-          <t>Hoàn thành Nhiệm Vụ Chính "Điều Gì Nung Nấu Dưới Lãnh Nguyên"</t>
+          <t>Hoàn thành Nhiệm Vụ Chính "Lửa Cháy Dưới Băng Giá"</t>
         </is>
       </c>
       <c r="N168" t="inlineStr">
@@ -12404,7 +12404,7 @@
       </c>
       <c r="M171" t="inlineStr">
         <is>
-          <t>Live Operations</t>
+          <t>Hoạt Động Trực Tuyến</t>
         </is>
       </c>
       <c r="N171" t="inlineStr">
@@ -12474,7 +12474,7 @@
       </c>
       <c r="M172" t="inlineStr">
         <is>
-          <t>Hoàn thành Nhiệm Vụ "Giai Điệu Lạc Trôi"</t>
+          <t>Hoàn thành Nhiệm vụ "Giai điệu thất lạc"</t>
         </is>
       </c>
       <c r="N172" t="inlineStr">
@@ -12544,7 +12544,7 @@
       </c>
       <c r="M173" t="inlineStr">
         <is>
-          <t>Hoàn thành Nhiệm Vụ "Thợ Săn Cơ Giới Vô Địch"</t>
+          <t>Hoàn thành Nhiệm vụ "Kẻ trinh sát cơ khí vô song"</t>
         </is>
       </c>
       <c r="N173" t="inlineStr">
@@ -12684,7 +12684,7 @@
       </c>
       <c r="M175" t="inlineStr">
         <is>
-          <t>Deliver Soliseeds</t>
+          <t>Giao Hạt Soliseed</t>
         </is>
       </c>
       <c r="N175" t="inlineStr">
@@ -12754,7 +12754,7 @@
       </c>
       <c r="M176" t="inlineStr">
         <is>
-          <t>Hoàn thành Nhiệm Vụ "Nơi Ánh Sáng Hóa Hình"</t>
+          <t>Hoàn thành Nhiệm vụ "Nơi ánh sáng định hình"</t>
         </is>
       </c>
       <c r="N176" t="inlineStr">
@@ -12824,7 +12824,7 @@
       </c>
       <c r="M177" t="inlineStr">
         <is>
-          <t>Thu thập Băng Ghi Lời Cuối</t>
+          <t>Thu thập Những Cuộn Băng Lời Trăn Trối.</t>
         </is>
       </c>
       <c r="N177" t="inlineStr">
@@ -12894,7 +12894,7 @@
       </c>
       <c r="M178" t="inlineStr">
         <is>
-          <t>Hoàn thành Nhiệm Vụ "Không Chỉ Là Trang Trí"</t>
+          <t>Hoàn thành Nhiệm vụ "Không chỉ là trang trí"</t>
         </is>
       </c>
       <c r="N178" t="inlineStr">
@@ -12964,7 +12964,7 @@
       </c>
       <c r="M179" t="inlineStr">
         <is>
-          <t>Hoàn thành tất cả nhiệm vụ tăng cường Bão Hư Không</t>
+          <t>Hoàn thành tất cả nhiệm vụ Tăng Cường Bão Hư Không.</t>
         </is>
       </c>
       <c r="N179" t="inlineStr">
@@ -13034,7 +13034,7 @@
       </c>
       <c r="M180" t="inlineStr">
         <is>
-          <t>Hoàn thành Nhiệm Vụ "Đài Thiên Văn Spacetrek: Giai Đoạn Giám Sát"</t>
+          <t>Hoàn thành Nhiệm vụ "Đài quan sát Spacetrek: Giai đoạn Giám sát"</t>
         </is>
       </c>
       <c r="N180" t="inlineStr">
@@ -13104,7 +13104,7 @@
       </c>
       <c r="M181" t="inlineStr">
         <is>
-          <t>Hoàn thành Nhiệm vụ "Trở về Ánh sáng"</t>
+          <t>Hoàn thành Nhiệm vụ "Trở về với Ánh sáng"</t>
         </is>
       </c>
       <c r="N181" t="inlineStr">
@@ -13314,7 +13314,7 @@
       </c>
       <c r="M184" t="inlineStr">
         <is>
-          <t>Nâng cấp Cấp độ Chế tác Xe</t>
+          <t>Nâng Cấp Cấp Độ Cải Tiến Phương Tiện</t>
         </is>
       </c>
       <c r="N184" t="inlineStr">
@@ -14294,7 +14294,7 @@
       </c>
       <c r="M198" t="inlineStr">
         <is>
-          <t>Styling Guide</t>
+          <t>Hướng Dẫn Phong Cách</t>
         </is>
       </c>
       <c r="N198" t="inlineStr">
@@ -14364,7 +14364,7 @@
       </c>
       <c r="M199" t="inlineStr">
         <is>
-          <t>Startorch Academy News</t>
+          <t>Tin tức Học viện Startorch</t>
         </is>
       </c>
       <c r="N199" t="inlineStr">
@@ -14434,7 +14434,7 @@
       </c>
       <c r="M200" t="inlineStr">
         <is>
-          <t>&lt;i&gt;Báo cáo Điều tra Bóng tối Học viện Startorch Số AN25360&lt;/i&gt;</t>
+          <t>&lt;i&gt;Báo cáo Điều tra Mặt Tối Học viện Startorch Số AN25360&lt;/i&gt;</t>
         </is>
       </c>
       <c r="N200" t="inlineStr">
@@ -14854,7 +14854,7 @@
       </c>
       <c r="M206" t="inlineStr">
         <is>
-          <t>"Little Savior"</t>
+          <t>"Vị Cứu Tinh Nhỏ"</t>
         </is>
       </c>
       <c r="N206" t="inlineStr">
@@ -14924,7 +14924,7 @@
       </c>
       <c r="M207" t="inlineStr">
         <is>
-          <t>Custom Accessory</t>
+          <t>Trang Sức Tùy Chỉnh</t>
         </is>
       </c>
       <c r="N207" t="inlineStr">
@@ -14994,7 +14994,7 @@
       </c>
       <c r="M208" t="inlineStr">
         <is>
-          <t>Factory New</t>
+          <t>Mới tinh</t>
         </is>
       </c>
       <c r="N208" t="inlineStr">
@@ -15064,7 +15064,7 @@
       </c>
       <c r="M209" t="inlineStr">
         <is>
-          <t>Ngôi Sao Hành Trình</t>
+          <t>Ngôi Sao Lang Thang</t>
         </is>
       </c>
       <c r="N209" t="inlineStr">
@@ -15134,7 +15134,7 @@
       </c>
       <c r="M210" t="inlineStr">
         <is>
-          <t>Tiêu Chuẩn Chassis</t>
+          <t>Khung Xe Tiêu Chuẩn</t>
         </is>
       </c>
       <c r="N210" t="inlineStr">
@@ -15204,7 +15204,7 @@
       </c>
       <c r="M211" t="inlineStr">
         <is>
-          <t>Custom Chassis</t>
+          <t>Khung Xe Tùy Chỉnh</t>
         </is>
       </c>
       <c r="N211" t="inlineStr">
@@ -16604,7 +16604,7 @@
       </c>
       <c r="M231" t="inlineStr">
         <is>
-          <t>Ca sĩ Không gian Sâu</t>
+          <t>Ca sĩ Không Gian Sâu</t>
         </is>
       </c>
       <c r="N231" t="inlineStr">
@@ -16744,7 +16744,7 @@
       </c>
       <c r="M233" t="inlineStr">
         <is>
-          <t>Observer's Eye</t>
+          <t>Con Mắt Người Quan Sát</t>
         </is>
       </c>
       <c r="N233" t="inlineStr">
@@ -16814,7 +16814,7 @@
       </c>
       <c r="M234" t="inlineStr">
         <is>
-          <t>Silent Array</t>
+          <t>Mảng Im Lặng</t>
         </is>
       </c>
       <c r="N234" t="inlineStr">
@@ -16884,7 +16884,7 @@
       </c>
       <c r="M235" t="inlineStr">
         <is>
-          <t>Flash Freeze</t>
+          <t>Đóng Băng Tức Thời</t>
         </is>
       </c>
       <c r="N235" t="inlineStr">
@@ -16954,7 +16954,7 @@
       </c>
       <c r="M236" t="inlineStr">
         <is>
-          <t>Ingenuity</t>
+          <t>Khéo léo</t>
         </is>
       </c>
       <c r="N236" t="inlineStr">
@@ -17024,7 +17024,7 @@
       </c>
       <c r="M237" t="inlineStr">
         <is>
-          <t>On Thin Ice</t>
+          <t>Đứng Trên Lưỡi Dao</t>
         </is>
       </c>
       <c r="N237" t="inlineStr">
@@ -17094,7 +17094,7 @@
       </c>
       <c r="M238" t="inlineStr">
         <is>
-          <t>Flux Wings</t>
+          <t>Đôi cánh Luân Lưu</t>
         </is>
       </c>
       <c r="N238" t="inlineStr">
@@ -17164,7 +17164,7 @@
       </c>
       <c r="M239" t="inlineStr">
         <is>
-          <t>Đi theo Ánh Mặt trời</t>
+          <t>Đi theo Ánh Mặt Trời</t>
         </is>
       </c>
       <c r="N239" t="inlineStr">
@@ -17234,7 +17234,7 @@
       </c>
       <c r="M240" t="inlineStr">
         <is>
-          <t>Cô gái với Exostrider</t>
+          <t>Cô gái cùng Exostrider</t>
         </is>
       </c>
       <c r="N240" t="inlineStr">
@@ -17374,7 +17374,7 @@
       </c>
       <c r="M242" t="inlineStr">
         <is>
-          <t>Horizon Lookout</t>
+          <t>Đài Quan Sát Chân Trời</t>
         </is>
       </c>
       <c r="N242" t="inlineStr">
@@ -17444,7 +17444,7 @@
       </c>
       <c r="M243" t="inlineStr">
         <is>
-          <t>Wuther như Một</t>
+          <t>Hợp Nhất Với Vực Gió</t>
         </is>
       </c>
       <c r="N243" t="inlineStr">
@@ -17584,7 +17584,7 @@
       </c>
       <c r="M245" t="inlineStr">
         <is>
-          <t>TERM-X: Outreach</t>
+          <t>TERM-X: Truyền Tin</t>
         </is>
       </c>
       <c r="N245" t="inlineStr">
@@ -17654,7 +17654,7 @@
       </c>
       <c r="M246" t="inlineStr">
         <is>
-          <t>Moonlit Path</t>
+          <t>Con Đường Ánh Trăng</t>
         </is>
       </c>
       <c r="N246" t="inlineStr">
@@ -17724,7 +17724,7 @@
       </c>
       <c r="M247" t="inlineStr">
         <is>
-          <t>Hoàn thành Nhiệm vụ "Phá vỡ Tấm Gương Băng giá"</t>
+          <t>Hoàn thành Nhiệm vụ "Phá vỡ Tấm gương băng giá"</t>
         </is>
       </c>
       <c r="N247" t="inlineStr">
@@ -17794,7 +17794,7 @@
       </c>
       <c r="M248" t="inlineStr">
         <is>
-          <t>Giải tất cả câu đố Smartprint Cube trên Bề mặt Frostlands</t>
+          <t>Giải tất cả các câu đố Smartprint Cube trên Bề Mặt Frostlands</t>
         </is>
       </c>
       <c r="N248" t="inlineStr">
@@ -17864,7 +17864,7 @@
       </c>
       <c r="M249" t="inlineStr">
         <is>
-          <t>Hoàn thành Nhiệm vụ "Bản nhạc của Băng và Thép"</t>
+          <t>Hoàn thành Nhiệm vụ "Khúc ca băng và thép"</t>
         </is>
       </c>
       <c r="N249" t="inlineStr">
@@ -17934,7 +17934,7 @@
       </c>
       <c r="M250" t="inlineStr">
         <is>
-          <t>Hoàn thành Afterstory "Tất cả Những gì Ánh Mặt trời Chạm tới"</t>
+          <t>Hoàn thành Câu Chuyện Sau "Ánh Nắng Chạm Đến Mọi Thứ"</t>
         </is>
       </c>
       <c r="N250" t="inlineStr">
@@ -18564,7 +18564,7 @@
       </c>
       <c r="M259" t="inlineStr">
         <is>
-          <t>Tới Vùng Đất Tuyết</t>
+          <t>Đến Vùng Đất Tuyết</t>
         </is>
       </c>
       <c r="N259" t="inlineStr">
@@ -18634,7 +18634,7 @@
       </c>
       <c r="M260" t="inlineStr">
         <is>
-          <t>A Small Miracle</t>
+          <t>Một Phép Màu Nhỏ</t>
         </is>
       </c>
       <c r="N260" t="inlineStr">
@@ -18704,7 +18704,7 @@
       </c>
       <c r="M261" t="inlineStr">
         <is>
-          <t>Voyaging Star's Farewell</t>
+          <t>Lời Tạm Biệt Ngôi Sao Lang Thang</t>
         </is>
       </c>
       <c r="N261" t="inlineStr">
@@ -18844,7 +18844,7 @@
       </c>
       <c r="M263" t="inlineStr">
         <is>
-          <t>Into Falling Snow</t>
+          <t>Vào Tuyết Rơi</t>
         </is>
       </c>
       <c r="N263" t="inlineStr">
@@ -18914,7 +18914,7 @@
       </c>
       <c r="M264" t="inlineStr">
         <is>
-          <t>Where Snow Can't Reach</t>
+          <t>Nơi Tuyết Không Thể Chạm Tới</t>
         </is>
       </c>
       <c r="N264" t="inlineStr">
@@ -18984,7 +18984,7 @@
       </c>
       <c r="M265" t="inlineStr">
         <is>
-          <t>A Long, Long Winter</t>
+          <t>Mùa Đông Dài Đằng Đẵng</t>
         </is>
       </c>
       <c r="N265" t="inlineStr">
@@ -19054,7 +19054,7 @@
       </c>
       <c r="M266" t="inlineStr">
         <is>
-          <t>Delayed Spring</t>
+          <t>Mùa xuân trì hoãn</t>
         </is>
       </c>
       <c r="N266" t="inlineStr">
@@ -19194,7 +19194,7 @@
       </c>
       <c r="M268" t="inlineStr">
         <is>
-          <t>A Silent Watcher</t>
+          <t>Người Quan Sát Vô Thanh</t>
         </is>
       </c>
       <c r="N268" t="inlineStr">
@@ -19334,7 +19334,7 @@
       </c>
       <c r="M270" t="inlineStr">
         <is>
-          <t>Biển Hoa Đóng Băng</t>
+          <t>Biển Hoa Đông Cứng</t>
         </is>
       </c>
       <c r="N270" t="inlineStr">
@@ -19404,7 +19404,7 @@
       </c>
       <c r="M271" t="inlineStr">
         <is>
-          <t>A Forest Waking Up</t>
+          <t>Khu Rừng Thức Giấc</t>
         </is>
       </c>
       <c r="N271" t="inlineStr">
@@ -19474,7 +19474,7 @@
       </c>
       <c r="M272" t="inlineStr">
         <is>
-          <t>A Forest Buried Deep</t>
+          <t>Khu Rừng Vùi Sâu</t>
         </is>
       </c>
       <c r="N272" t="inlineStr">
@@ -19614,7 +19614,7 @@
       </c>
       <c r="M274" t="inlineStr">
         <is>
-          <t>What Cô ấy Longs For</t>
+          <t>Điều Nàng Khát Khao</t>
         </is>
       </c>
       <c r="N274" t="inlineStr">
@@ -19684,7 +19684,7 @@
       </c>
       <c r="M275" t="inlineStr">
         <is>
-          <t>Starlit Lullaby</t>
+          <t>Khúc Ru Sao Đêm</t>
         </is>
       </c>
       <c r="N275" t="inlineStr">
@@ -19754,7 +19754,7 @@
       </c>
       <c r="M276" t="inlineStr">
         <is>
-          <t>Lake Where Causality Halts</t>
+          <t>Hồ Nơi Nhân Quả Dừng Lại</t>
         </is>
       </c>
       <c r="N276" t="inlineStr">
@@ -20594,7 +20594,7 @@
       </c>
       <c r="M288" t="inlineStr">
         <is>
-          <t>Nameless Explorer</t>
+          <t>Nhà Thám Hiểm Vô Danh</t>
         </is>
       </c>
       <c r="N288" t="inlineStr">
@@ -20734,7 +20734,7 @@
       </c>
       <c r="M290" t="inlineStr">
         <is>
-          <t>Nameless Explorer - Early Access</t>
+          <t>Nhà Thám Hiểm Vô Danh - Truy Cập Sớm</t>
         </is>
       </c>
       <c r="N290" t="inlineStr">
@@ -20944,7 +20944,7 @@
       </c>
       <c r="M293" t="inlineStr">
         <is>
-          <t>Denia - Early Access</t>
+          <t>Denia - Truy Cập Sớm</t>
         </is>
       </c>
       <c r="N293" t="inlineStr">
@@ -21014,7 +21014,7 @@
       </c>
       <c r="M294" t="inlineStr">
         <is>
-          <t>Lộ Trình Sao Đan Xen</t>
+          <t>Những Con Đường Sao Đan Xen</t>
         </is>
       </c>
       <c r="N294" t="inlineStr">
@@ -21994,7 +21994,7 @@
       </c>
       <c r="M308" t="inlineStr">
         <is>
-          <t>Startorch Dành Cho Bạn</t>
+          <t>Sao Chổi Dành Cho Bạn</t>
         </is>
       </c>
       <c r="N308" t="inlineStr">
@@ -23884,7 +23884,7 @@
       </c>
       <c r="M335" t="inlineStr">
         <is>
-          <t>Hoàn Thành Nhiệm Vụ Chính Chương III Hồi V</t>
+          <t>Hoàn thành Chương III Hồi V trong Nhiệm Vụ Chính</t>
         </is>
       </c>
       <c r="N335" t="inlineStr">
@@ -23954,7 +23954,7 @@
       </c>
       <c r="M336" t="inlineStr">
         <is>
-          <t>QUEEN</t>
+          <t>NỮ HOÀNG</t>
         </is>
       </c>
       <c r="N336" t="inlineStr">
@@ -24094,7 +24094,7 @@
       </c>
       <c r="M338" t="inlineStr">
         <is>
-          <t>Lời Gọi Từ Vượt Ngôi Sao</t>
+          <t>Tiếng Gọi Từ Vượt Ngôi Sao</t>
         </is>
       </c>
       <c r="N338" t="inlineStr">
@@ -24164,7 +24164,7 @@
       </c>
       <c r="M339" t="inlineStr">
         <is>
-          <t>Tan Vào Tuyết Xanh Coban</t>
+          <t>Tan vào Tuyết Xanh Coban</t>
         </is>
       </c>
       <c r="N339" t="inlineStr">
@@ -24234,7 +24234,7 @@
       </c>
       <c r="M340" t="inlineStr">
         <is>
-          <t>Sau khi Party Smiles</t>
+          <t>Nụ Cười Sau Bữa Tiệc</t>
         </is>
       </c>
       <c r="N340" t="inlineStr">
@@ -24374,7 +24374,7 @@
       </c>
       <c r="M342" t="inlineStr">
         <is>
-          <t>Thử thách lặp lại "Endstate Matrix: Vòng Luân Hồi Tận Thế"</t>
+          <t>Thử Thách Lặp Lại "Ma Trận Tận Thế: Vòng Luân Hồi Hủy Diệt"</t>
         </is>
       </c>
       <c r="N342" t="inlineStr">
@@ -24444,7 +24444,7 @@
       </c>
       <c r="M343" t="inlineStr">
         <is>
-          <t>Hoàn thành "Gold Suspended in Shadows"</t>
+          <t>Hoàn thành "Vàng Pha Bóng Tối".</t>
         </is>
       </c>
       <c r="N343" t="inlineStr">
@@ -24514,7 +24514,7 @@
       </c>
       <c r="M344" t="inlineStr">
         <is>
-          <t>Hoàn thành "A Snowbound Order from Cobalt Blue"</t>
+          <t>Hoàn thành "Lệnh Tuyết Phong Từ Cobalt Blue."</t>
         </is>
       </c>
       <c r="N344" t="inlineStr">
@@ -24584,7 +24584,7 @@
       </c>
       <c r="M345" t="inlineStr">
         <is>
-          <t>"Whispers Between Stars" Event</t>
+          <t>"Sự kiện \"Lời Thì Thầm Giữa Các Vì Sao\""</t>
         </is>
       </c>
       <c r="N345" t="inlineStr">
@@ -24864,7 +24864,7 @@
       </c>
       <c r="M349" t="inlineStr">
         <is>
-          <t>Snowfluff Seal</t>
+          <t>Ấn Chương Bông Tuyết</t>
         </is>
       </c>
       <c r="N349" t="inlineStr">
@@ -24934,7 +24934,7 @@
       </c>
       <c r="M350" t="inlineStr">
         <is>
-          <t>Stillmind</t>
+          <t>Tĩnh Tâm</t>
         </is>
       </c>
       <c r="N350" t="inlineStr">
@@ -25004,7 +25004,7 @@
       </c>
       <c r="M351" t="inlineStr">
         <is>
-          <t>Denia's Doll</t>
+          <t>Búp Bê Của Denia</t>
         </is>
       </c>
       <c r="N351" t="inlineStr">
@@ -25074,7 +25074,7 @@
       </c>
       <c r="M352" t="inlineStr">
         <is>
-          <t>Gilded Expectations</t>
+          <t>Kỳ Vọng Mạ Vàng</t>
         </is>
       </c>
       <c r="N352" t="inlineStr">
@@ -25144,7 +25144,7 @@
       </c>
       <c r="M353" t="inlineStr">
         <is>
-          <t>Đến với Ánh Vàng Ấm Áp</t>
+          <t>Đến Ánh Vàng Ấm Áp</t>
         </is>
       </c>
       <c r="N353" t="inlineStr">
@@ -25214,7 +25214,7 @@
       </c>
       <c r="M354" t="inlineStr">
         <is>
-          <t>Sự Tan Vỡ của Ảo Giác</t>
+          <t>Sự Sụp Đổ Của Ảo Vọng</t>
         </is>
       </c>
       <c r="N354" t="inlineStr">
@@ -25284,7 +25284,7 @@
       </c>
       <c r="M355" t="inlineStr">
         <is>
-          <t>Running Towards Startorch</t>
+          <t>Chạy Về Hướng Startorch</t>
         </is>
       </c>
       <c r="N355" t="inlineStr">
@@ -25354,7 +25354,7 @@
       </c>
       <c r="M356" t="inlineStr">
         <is>
-          <t>Khoảnh Khắc của Bình Minh Rạng Rỡ</t>
+          <t>Khoảnh khắc bình minh rạng rỡ</t>
         </is>
       </c>
       <c r="N356" t="inlineStr">
@@ -25424,7 +25424,7 @@
       </c>
       <c r="M357" t="inlineStr">
         <is>
-          <t>Khoảnh Khắc của Hoàng Hôn Yên Bình</t>
+          <t>Khoảnh khắc hoàng hôn yên bình</t>
         </is>
       </c>
       <c r="N357" t="inlineStr">
@@ -25494,7 +25494,7 @@
       </c>
       <c r="M358" t="inlineStr">
         <is>
-          <t>Bóng Tối Theo Sau Bạn</t>
+          <t>Bóng Đuổi Theo</t>
         </is>
       </c>
       <c r="N358" t="inlineStr">
@@ -25704,7 +25704,7 @@
       </c>
       <c r="M361" t="inlineStr">
         <is>
-          <t>Hoshi To Bokura To</t>
+          <t>Hoshi, Chúng Ta và...</t>
         </is>
       </c>
       <c r="N361" t="inlineStr">
@@ -25774,7 +25774,7 @@
       </c>
       <c r="M362" t="inlineStr">
         <is>
-          <t>Last Surprise</t>
+          <t>Điều Bất Ngờ Cuối Cùng</t>
         </is>
       </c>
       <c r="N362" t="inlineStr">
@@ -25844,7 +25844,7 @@
       </c>
       <c r="M363" t="inlineStr">
         <is>
-          <t>Dòng Sông trong Sa Mạc</t>
+          <t>Dòng Sông Giữa Sa Mạc</t>
         </is>
       </c>
       <c r="N363" t="inlineStr">
@@ -25914,7 +25914,7 @@
       </c>
       <c r="M364" t="inlineStr">
         <is>
-          <t>Persona 5 Royal: Collab Track</t>
+          <t>Bài Hát Hợp Tác: Persona 5 Royal</t>
         </is>
       </c>
       <c r="N364" t="inlineStr">
@@ -25984,7 +25984,7 @@
       </c>
       <c r="M365" t="inlineStr">
         <is>
-          <t>Persona 5 Royal: Collab Track</t>
+          <t>Bài Hát Hợp Tác: Persona 5 Royal</t>
         </is>
       </c>
       <c r="N365" t="inlineStr">
@@ -26054,7 +26054,7 @@
       </c>
       <c r="M366" t="inlineStr">
         <is>
-          <t>Persona 5 Royal: Collab Track</t>
+          <t>Bài Hát Hợp Tác: Persona 5 Royal</t>
         </is>
       </c>
       <c r="N366" t="inlineStr">
@@ -26824,7 +26824,7 @@
       </c>
       <c r="M377" t="inlineStr">
         <is>
-          <t>Flowers For Bạn</t>
+          <t>Những Bông Hoa Dành Tặng Em</t>
         </is>
       </c>
       <c r="N377" t="inlineStr">
@@ -26894,7 +26894,7 @@
       </c>
       <c r="M378" t="inlineStr">
         <is>
-          <t>Resident Evil</t>
+          <t>Cư dân ác mộng</t>
         </is>
       </c>
       <c r="N378" t="inlineStr">
@@ -27244,7 +27244,7 @@
       </c>
       <c r="M383" t="inlineStr">
         <is>
-          <t>Kaiju Không. 8</t>
+          <t>Kaiju Số 8</t>
         </is>
       </c>
       <c r="N383" t="inlineStr">
@@ -27314,7 +27314,7 @@
       </c>
       <c r="M384" t="inlineStr">
         <is>
-          <t>Riders Republic</t>
+          <t>Cộng Hòa Kỵ Sĩ</t>
         </is>
       </c>
       <c r="N384" t="inlineStr">
@@ -27384,7 +27384,7 @@
       </c>
       <c r="M385" t="inlineStr">
         <is>
-          <t>Angry Birds</t>
+          <t>Những chú chim giận dữ</t>
         </is>
       </c>
       <c r="N385" t="inlineStr">
@@ -27454,7 +27454,7 @@
       </c>
       <c r="M386" t="inlineStr">
         <is>
-          <t>Vùng Xa Xôi của Aurora</t>
+          <t>Viễn Xứ Aurora</t>
         </is>
       </c>
       <c r="N386" t="inlineStr">
@@ -27524,7 +27524,7 @@
       </c>
       <c r="M387" t="inlineStr">
         <is>
-          <t>Ever True</t>
+          <t>Vĩnh Hằng Trung Thành</t>
         </is>
       </c>
       <c r="N387" t="inlineStr">
@@ -27594,7 +27594,7 @@
       </c>
       <c r="M388" t="inlineStr">
         <is>
-          <t>Lời Hứa Là Phải Giữ</t>
+          <t>Lời Hứa Là Sẽ Giao, Bạn Nhé</t>
         </is>
       </c>
       <c r="N388" t="inlineStr">
@@ -27664,7 +27664,7 @@
       </c>
       <c r="M389" t="inlineStr">
         <is>
-          <t>Tỏa Sáng vào Vực Sâu</t>
+          <t>Thâm Nhập Vào Vực Sâu</t>
         </is>
       </c>
       <c r="N389" t="inlineStr">
@@ -27734,7 +27734,7 @@
       </c>
       <c r="M390" t="inlineStr">
         <is>
-          <t>Where This Heart Comes From</t>
+          <t>Nơi Trái Tim Ta Thuộc Về</t>
         </is>
       </c>
       <c r="N390" t="inlineStr">
@@ -27804,7 +27804,7 @@
       </c>
       <c r="M391" t="inlineStr">
         <is>
-          <t>Seamless</t>
+          <t>Hoàn hảo</t>
         </is>
       </c>
       <c r="N391" t="inlineStr">
@@ -27874,7 +27874,7 @@
       </c>
       <c r="M392" t="inlineStr">
         <is>
-          <t>Crystal Sky</t>
+          <t>Bầu Trời Pha Lê</t>
         </is>
       </c>
       <c r="N392" t="inlineStr">
@@ -27944,7 +27944,7 @@
       </c>
       <c r="M393" t="inlineStr">
         <is>
-          <t>Hiyuki Cube</t>
+          <t>Khối Lập Phương Hiyuki</t>
         </is>
       </c>
       <c r="N393" t="inlineStr">
@@ -28014,7 +28014,7 @@
       </c>
       <c r="M394" t="inlineStr">
         <is>
-          <t>Bountiful Waves</t>
+          <t>Sóng Dạt Dào</t>
         </is>
       </c>
       <c r="N394" t="inlineStr">
@@ -28084,7 +28084,7 @@
       </c>
       <c r="M395" t="inlineStr">
         <is>
-          <t>Second Coming of Solaris: Mùa Cộng Tác</t>
+          <t>Sự Trở Lại Của Solaris: Mùa Cộng Tác</t>
         </is>
       </c>
       <c r="N395" t="inlineStr">
@@ -28154,7 +28154,7 @@
       </c>
       <c r="M396" t="inlineStr">
         <is>
-          <t>Hoàn thành Nhiệm vụ Thám hiểm "Một Ngày Hoàn Hảo để Bay"</t>
+          <t>Hoàn thành Nhiệm Vụ Thám Hiểm "Một Ngày Tuyệt Vời Để Bay Lượn"</t>
         </is>
       </c>
       <c r="N396" t="inlineStr">
@@ -28224,7 +28224,7 @@
       </c>
       <c r="M397" t="inlineStr">
         <is>
-          <t>Hoàn thành Nhiệm vụ Thám hiểm "Trái Tim Dimmr Vỡ"</t>
+          <t>Hoàn thành Nhiệm Vụ Thám Hiểm "Trái Tim Dimmu Vỡ Nát"</t>
         </is>
       </c>
       <c r="N397" t="inlineStr">
@@ -28294,7 +28294,7 @@
       </c>
       <c r="M398" t="inlineStr">
         <is>
-          <t>Chứng kiến sự ra đời của nguyên mẫu xe máy thám hiểm</t>
+          <t>Chứng kiến sự ra đời của nguyên mẫu xe máy thám hiểm.</t>
         </is>
       </c>
       <c r="N398" t="inlineStr">
@@ -28364,7 +28364,7 @@
       </c>
       <c r="M399" t="inlineStr">
         <is>
-          <t>Sự kiện "Into the Land of Paradox"</t>
+          <t>"Sự kiện "Vào Vùng Đất Nghịch Lý""</t>
         </is>
       </c>
       <c r="N399" t="inlineStr">
@@ -28434,7 +28434,7 @@
       </c>
       <c r="M400" t="inlineStr">
         <is>
-          <t>Hoàn thành Nhiệm vụ Chính "Ánh Sao từ Ngày Xưa"</t>
+          <t>Hoàn thành Nhiệm vụ Chính "Ánh Sao Từ Những Ngày Xưa"</t>
         </is>
       </c>
       <c r="N400" t="inlineStr">
@@ -28504,7 +28504,7 @@
       </c>
       <c r="M401" t="inlineStr">
         <is>
-          <t>Hoàn thành "Beneath a Melting Night Sky"</t>
+          <t>Hoàn thành "Dưới Bầu Trời Đêm Tan Băng."</t>
         </is>
       </c>
       <c r="N401" t="inlineStr">
@@ -28574,7 +28574,7 @@
       </c>
       <c r="M402" t="inlineStr">
         <is>
-          <t>Nảy Bóng Sao</t>
+          <t>Vụ nổ sao</t>
         </is>
       </c>
       <c r="N402" t="inlineStr">
@@ -30814,7 +30814,7 @@
       </c>
       <c r="M434" t="inlineStr">
         <is>
-          <t>Dưới Những Vì Sao Của Đêm Xưa</t>
+          <t>Dưới Những Vì Sao Đêm Xưa</t>
         </is>
       </c>
       <c r="N434" t="inlineStr">
@@ -30884,7 +30884,7 @@
       </c>
       <c r="M435" t="inlineStr">
         <is>
-          <t>Lời Thì Thầm Trong Rừng</t>
+          <t>Lời thì thầm trong rừng sâu</t>
         </is>
       </c>
       <c r="N435" t="inlineStr">
@@ -31024,7 +31024,7 @@
       </c>
       <c r="M437" t="inlineStr">
         <is>
-          <t>Khu Rừng Khi Hoàng Hôn Kết Thúc</t>
+          <t>Rừng Hoàng Hôn</t>
         </is>
       </c>
       <c r="N437" t="inlineStr">
@@ -31094,7 +31094,7 @@
       </c>
       <c r="M438" t="inlineStr">
         <is>
-          <t>Evening Light, Morning Glow</t>
+          <t>Ánh Chiều Tà, Rạng Đông</t>
         </is>
       </c>
       <c r="N438" t="inlineStr">
@@ -31164,7 +31164,7 @@
       </c>
       <c r="M439" t="inlineStr">
         <is>
-          <t>A Comforting Night</t>
+          <t>Đêm Bình Yên</t>
         </is>
       </c>
       <c r="N439" t="inlineStr">
@@ -31234,7 +31234,7 @@
       </c>
       <c r="M440" t="inlineStr">
         <is>
-          <t>Trở Lại Vào Lúc Kết Thúc</t>
+          <t>Quay lại khi kết thúc</t>
         </is>
       </c>
       <c r="N440" t="inlineStr">
@@ -31304,7 +31304,7 @@
       </c>
       <c r="M441" t="inlineStr">
         <is>
-          <t>The Vastness Before Us</t>
+          <t>Vùng Đất Bao La Trước Mắt</t>
         </is>
       </c>
       <c r="N441" t="inlineStr">
@@ -31374,7 +31374,7 @@
       </c>
       <c r="M442" t="inlineStr">
         <is>
-          <t>The Watchers</t>
+          <t>Những Kẻ Canh Gác</t>
         </is>
       </c>
       <c r="N442" t="inlineStr">
@@ -31444,7 +31444,7 @@
       </c>
       <c r="M443" t="inlineStr">
         <is>
-          <t>Ngôi Sao Trở Về Từ Vô Tận</t>
+          <t>Ngôi Sao Về Nhà Từ Vô Định</t>
         </is>
       </c>
       <c r="N443" t="inlineStr">
@@ -31514,7 +31514,7 @@
       </c>
       <c r="M444" t="inlineStr">
         <is>
-          <t>Trái Tim Của Lahai-Roi</t>
+          <t>Trái Tim Lahai-Roi</t>
         </is>
       </c>
       <c r="N444" t="inlineStr">
@@ -31584,7 +31584,7 @@
       </c>
       <c r="M445" t="inlineStr">
         <is>
-          <t>Khi Tuyết Tan Thành Mùa Xuân</t>
+          <t>Khi Tuyết Tan Thành Xuân</t>
         </is>
       </c>
       <c r="N445" t="inlineStr">
@@ -31654,7 +31654,7 @@
       </c>
       <c r="M446" t="inlineStr">
         <is>
-          <t>Hơi Ấm Còn Lại Của Giấc Mơ</t>
+          <t>Hơi Ấm Lưu Luyến Của Giấc Mơ</t>
         </is>
       </c>
       <c r="N446" t="inlineStr">
@@ -31724,7 +31724,7 @@
       </c>
       <c r="M447" t="inlineStr">
         <is>
-          <t>Đêm Cuối Cùng Ở Lahai-Roi</t>
+          <t>Đêm Cuối Cùng ở Lahai-Roi</t>
         </is>
       </c>
       <c r="N447" t="inlineStr">
@@ -31794,7 +31794,7 @@
       </c>
       <c r="M448" t="inlineStr">
         <is>
-          <t>Điều Đợi Chờ Ngoài Ánh Sáng</t>
+          <t>Điều Gì Đợi Chờ Ngoài Ánh Sáng Rực Rỡ</t>
         </is>
       </c>
       <c r="N448" t="inlineStr">
@@ -31864,7 +31864,7 @@
       </c>
       <c r="M449" t="inlineStr">
         <is>
-          <t>Sự Kiện Hạn Chế 2026 Quà Tặng Đại Kỷ Niệm</t>
+          <t>Sự Kiện Hạn Chế Quà Tặng Đại Kỷ Niệm 2026</t>
         </is>
       </c>
       <c r="N449" t="inlineStr">
@@ -31934,7 +31934,7 @@
       </c>
       <c r="M450" t="inlineStr">
         <is>
-          <t>Lời Phán Quyết Của Lưỡi Kiếm Đỏ Thẫm</t>
+          <t>Phán Quyết Của Lưỡi Kiếm Đỏ</t>
         </is>
       </c>
       <c r="N450" t="inlineStr">
@@ -32004,7 +32004,7 @@
       </c>
       <c r="M451" t="inlineStr">
         <is>
-          <t>Fading Foamlight</t>
+          <t>Ánh Sáng Bọt Nhạt Nhoà</t>
         </is>
       </c>
       <c r="N451" t="inlineStr">
@@ -32074,7 +32074,7 @@
       </c>
       <c r="M452" t="inlineStr">
         <is>
-          <t>Cô Gái Thất Bại</t>
+          <t>Cô Nàng Thất Bại</t>
         </is>
       </c>
       <c r="N452" t="inlineStr">
@@ -32144,7 +32144,7 @@
       </c>
       <c r="M453" t="inlineStr">
         <is>
-          <t>Người Bướm Huyền Thoại?</t>
+          <t>Người Bướm Đêm Huyền Thoại?</t>
         </is>
       </c>
       <c r="N453" t="inlineStr">
@@ -32284,7 +32284,7 @@
       </c>
       <c r="M455" t="inlineStr">
         <is>
-          <t>Moth Dust Allergy</t>
+          <t>Dị ứng Bụi Ngài</t>
         </is>
       </c>
       <c r="N455" t="inlineStr">
@@ -32914,7 +32914,7 @@
       </c>
       <c r="M464" t="inlineStr">
         <is>
-          <t>Stellar Orbit Beats</t>
+          <t>Nhịp Quỹ Đạo Tinh Tú</t>
         </is>
       </c>
       <c r="N464" t="inlineStr">
@@ -33124,7 +33124,7 @@
       </c>
       <c r="M467" t="inlineStr">
         <is>
-          <t>Phagosite: Voidarch</t>
+          <t>Phagosite: Hư Không Tể</t>
         </is>
       </c>
       <c r="N467" t="inlineStr">
@@ -33194,7 +33194,7 @@
       </c>
       <c r="M468" t="inlineStr">
         <is>
-          <t>Không thể tham gia sự kiện này ở Chế Độ Hợp Tác</t>
+          <t>Không thể tham gia sự kiện này trong Chế Độ Đồng Đội</t>
         </is>
       </c>
       <c r="N468" t="inlineStr">
@@ -33264,7 +33264,7 @@
       </c>
       <c r="M469" t="inlineStr">
         <is>
-          <t>Keystone</t>
+          <t>Đá Chìa Khóa</t>
         </is>
       </c>
       <c r="N469" t="inlineStr">
@@ -33334,7 +33334,7 @@
       </c>
       <c r="M470" t="inlineStr">
         <is>
-          <t>Track Status</t>
+          <t>Trạng Thái Theo Dõi</t>
         </is>
       </c>
       <c r="N470" t="inlineStr">
@@ -33474,7 +33474,7 @@
       </c>
       <c r="M472" t="inlineStr">
         <is>
-          <t>Startorch Academy Periodical Collection</t>
+          <t>Bộ sưu tập Tạp chí Học viện Startorch</t>
         </is>
       </c>
       <c r="N472" t="inlineStr">
@@ -33544,7 +33544,7 @@
       </c>
       <c r="M473" t="inlineStr">
         <is>
-          <t>Hospital Bed</t>
+          <t>Giường Bệnh</t>
         </is>
       </c>
       <c r="N473" t="inlineStr">
@@ -34804,7 +34804,7 @@
       </c>
       <c r="M491" t="inlineStr">
         <is>
-          <t>Quay về Lahai-Roi giữa Bão Hư Không</t>
+          <t>Trở lại Lahai-Roi giữa cơn Bão Hư Không</t>
         </is>
       </c>
       <c r="N491" t="inlineStr">
@@ -34874,7 +34874,7 @@
       </c>
       <c r="M492" t="inlineStr">
         <is>
-          <t>Quay về Viện Nghiên cứu bị khủng hoảng</t>
+          <t>Trở lại Viện Nghiên Cứu đang chìm trong khủng hoảng</t>
         </is>
       </c>
       <c r="N492" t="inlineStr">
@@ -35154,7 +35154,7 @@
       </c>
       <c r="M496" t="inlineStr">
         <is>
-          <t>Holographic Projection</t>
+          <t>Hình Hologram Phóng Đại</t>
         </is>
       </c>
       <c r="N496" t="inlineStr">
@@ -35224,7 +35224,7 @@
       </c>
       <c r="M497" t="inlineStr">
         <is>
-          <t>Không tìm thấy cấu hình phiên bản Vực Sâu Ảo Cảnh</t>
+          <t>Không tìm thấy cấu hình phiên bản Tổ Tacet Ảo Ảnh</t>
         </is>
       </c>
       <c r="N497" t="inlineStr">
@@ -35294,7 +35294,7 @@
       </c>
       <c r="M498" t="inlineStr">
         <is>
-          <t>Echo Ảo Cảnh trong Vực Sâu Ảo Cảnh bị khóa</t>
+          <t>Tổ Tacet Ảo Ảnh - Tiếng Vọng Ảo đã bị khóa</t>
         </is>
       </c>
       <c r="N498" t="inlineStr">
@@ -35364,7 +35364,7 @@
       </c>
       <c r="M499" t="inlineStr">
         <is>
-          <t>Resonator trong Vực Sâu Ảo Cảnh bị khóa</t>
+          <t>Tổ Tacet Ảo Ảnh - Resonator bị khóa</t>
         </is>
       </c>
       <c r="N499" t="inlineStr">
@@ -35434,7 +35434,7 @@
       </c>
       <c r="M500" t="inlineStr">
         <is>
-          <t>Tùy chọn Điều Chỉnh Nhiễm Sắc trong Vực Sâu Ảo Cảnh bị khóa</t>
+          <t>Tổ Tacet Ảo Ảnh - Tùy chọn Điều Chỉnh Meme bị khóa</t>
         </is>
       </c>
       <c r="N500" t="inlineStr">
@@ -35504,7 +35504,7 @@
       </c>
       <c r="M501" t="inlineStr">
         <is>
-          <t>Mid-air Attack 1</t>
+          <t>Tấn Công Giữa Không 1</t>
         </is>
       </c>
       <c r="N501" t="inlineStr">
